--- a/data_lake/industry/CFM/OEM SSD.xlsx
+++ b/data_lake/industry/CFM/OEM SSD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604E426A-D5A9-4C11-B8BB-84B4F502C5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2015A89E-3587-4366-854A-5F4D2B154DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -75,30 +75,30 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -107,9 +107,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -131,46 +136,46 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -452,19 +457,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.8984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -487,7 +493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -510,7 +516,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -533,7 +539,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -556,7 +562,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -579,7 +585,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -602,7 +608,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -625,7 +631,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -648,7 +654,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -671,7 +677,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -694,7 +700,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -717,7 +723,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -740,7 +746,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -763,7 +769,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -786,7 +792,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -809,7 +815,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -832,7 +838,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -855,7 +861,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -878,7 +884,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -901,7 +907,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -924,7 +930,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -947,7 +953,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -970,7 +976,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -993,7 +999,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1016,7 +1022,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1039,7 +1045,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1062,7 +1068,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1085,7 +1091,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1108,7 +1114,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1131,7 +1137,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1154,7 +1160,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1177,7 +1183,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1200,7 +1206,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1223,7 +1229,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1246,7 +1252,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1269,7 +1275,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1292,7 +1298,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1315,7 +1321,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1338,7 +1344,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1361,7 +1367,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -1384,7 +1390,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -1407,7 +1413,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -1430,7 +1436,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -1453,7 +1459,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -1476,7 +1482,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -1499,7 +1505,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -1522,7 +1528,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -1545,7 +1551,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -1565,6 +1571,121 @@
         <v>71</v>
       </c>
       <c r="G48" s="9">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>67</v>
+      </c>
+      <c r="F49" s="9">
+        <v>71</v>
+      </c>
+      <c r="G49" s="9">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>67</v>
+      </c>
+      <c r="F50" s="9">
+        <v>71</v>
+      </c>
+      <c r="G50" s="9">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>67</v>
+      </c>
+      <c r="F51" s="9">
+        <v>71</v>
+      </c>
+      <c r="G51" s="9">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>67</v>
+      </c>
+      <c r="F52" s="9">
+        <v>71</v>
+      </c>
+      <c r="G52" s="9">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>67</v>
+      </c>
+      <c r="F53" s="9">
+        <v>71</v>
+      </c>
+      <c r="G53" s="9">
         <v>68</v>
       </c>
     </row>
@@ -1576,19 +1697,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F473D36E-208F-4614-83B5-69AB6F33294E}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1611,7 +1732,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1634,7 +1755,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1657,7 +1778,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1680,7 +1801,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1703,7 +1824,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1726,7 +1847,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1749,7 +1870,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1772,7 +1893,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1795,7 +1916,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1818,7 +1939,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1841,7 +1962,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1864,7 +1985,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -1887,7 +2008,7 @@
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -1910,7 +2031,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -1933,7 +2054,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -1956,7 +2077,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -1979,7 +2100,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -2002,7 +2123,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2025,7 +2146,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2048,7 +2169,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2071,7 +2192,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2094,7 +2215,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2117,7 +2238,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2140,7 +2261,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2163,7 +2284,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2186,7 +2307,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2209,7 +2330,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2232,7 +2353,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2255,7 +2376,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2278,7 +2399,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2301,7 +2422,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2324,7 +2445,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2347,7 +2468,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2370,7 +2491,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2393,7 +2514,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2416,7 +2537,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2439,7 +2560,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2462,7 +2583,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2485,7 +2606,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -2508,7 +2629,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -2531,7 +2652,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -2554,7 +2675,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -2577,7 +2698,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -2600,7 +2721,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -2623,7 +2744,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -2646,7 +2767,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -2669,7 +2790,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -2689,6 +2810,121 @@
         <v>117</v>
       </c>
       <c r="G48" s="9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>110</v>
+      </c>
+      <c r="F49" s="9">
+        <v>117</v>
+      </c>
+      <c r="G49" s="9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>110</v>
+      </c>
+      <c r="F50" s="9">
+        <v>117</v>
+      </c>
+      <c r="G50" s="9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>110</v>
+      </c>
+      <c r="F51" s="9">
+        <v>117</v>
+      </c>
+      <c r="G51" s="9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>110</v>
+      </c>
+      <c r="F52" s="9">
+        <v>117</v>
+      </c>
+      <c r="G52" s="9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>110</v>
+      </c>
+      <c r="F53" s="9">
+        <v>117</v>
+      </c>
+      <c r="G53" s="9">
         <v>115</v>
       </c>
     </row>
@@ -2700,19 +2936,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6C0178-E414-47B2-A630-84DA7232A61F}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2735,7 +2971,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2758,7 +2994,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -2781,7 +3017,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -2804,7 +3040,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -2827,7 +3063,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -2850,7 +3086,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -2873,7 +3109,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -2896,7 +3132,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -2919,7 +3155,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -2942,7 +3178,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -2965,7 +3201,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -2988,7 +3224,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3011,7 +3247,7 @@
         <v>62.8</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3034,7 +3270,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3057,7 +3293,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3080,7 +3316,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3103,7 +3339,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3126,7 +3362,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3149,7 +3385,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3172,7 +3408,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3195,7 +3431,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3218,7 +3454,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3241,7 +3477,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3264,7 +3500,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3287,7 +3523,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3310,7 +3546,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3333,7 +3569,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3356,7 +3592,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3379,7 +3615,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3402,7 +3638,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3425,7 +3661,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3448,7 +3684,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3471,7 +3707,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3494,7 +3730,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3517,7 +3753,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3540,7 +3776,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3563,7 +3799,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3586,7 +3822,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3609,7 +3845,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -3632,7 +3868,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -3655,7 +3891,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -3678,7 +3914,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -3701,7 +3937,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -3724,7 +3960,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -3747,7 +3983,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -3770,7 +4006,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -3793,7 +4029,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -3813,6 +4049,121 @@
         <v>197</v>
       </c>
       <c r="G48" s="9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>193</v>
+      </c>
+      <c r="F49" s="9">
+        <v>197</v>
+      </c>
+      <c r="G49" s="9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>193</v>
+      </c>
+      <c r="F50" s="9">
+        <v>197</v>
+      </c>
+      <c r="G50" s="9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>193</v>
+      </c>
+      <c r="F51" s="9">
+        <v>197</v>
+      </c>
+      <c r="G51" s="9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>193</v>
+      </c>
+      <c r="F52" s="9">
+        <v>197</v>
+      </c>
+      <c r="G52" s="9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>193</v>
+      </c>
+      <c r="F53" s="9">
+        <v>197</v>
+      </c>
+      <c r="G53" s="9">
         <v>195</v>
       </c>
     </row>
@@ -3824,19 +4175,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE21688-DF7E-4F8C-887E-342649A09FB0}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.8984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3859,7 +4211,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -3882,7 +4234,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3905,7 +4257,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3928,7 +4280,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3951,7 +4303,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3974,7 +4326,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3997,7 +4349,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -4020,7 +4372,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -4043,7 +4395,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -4066,7 +4418,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -4089,7 +4441,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -4112,7 +4464,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -4135,7 +4487,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -4158,7 +4510,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -4181,7 +4533,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -4204,7 +4556,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -4227,7 +4579,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -4250,7 +4602,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -4273,7 +4625,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -4296,7 +4648,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -4319,7 +4671,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -4342,7 +4694,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -4365,7 +4717,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4388,7 +4740,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4411,7 +4763,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -4434,7 +4786,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -4457,7 +4809,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -4480,7 +4832,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -4503,7 +4855,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -4526,7 +4878,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -4549,7 +4901,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -4572,7 +4924,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -4595,7 +4947,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4618,7 +4970,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -4641,7 +4993,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -4664,7 +5016,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -4687,7 +5039,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -4710,7 +5062,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -4733,7 +5085,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -4756,7 +5108,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -4779,7 +5131,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -4802,7 +5154,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -4825,7 +5177,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -4848,7 +5200,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -4871,7 +5223,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -4894,7 +5246,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -4917,7 +5269,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -4937,6 +5289,121 @@
         <v>76</v>
       </c>
       <c r="G48" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>73.5</v>
+      </c>
+      <c r="F49" s="9">
+        <v>76</v>
+      </c>
+      <c r="G49" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>73.5</v>
+      </c>
+      <c r="F50" s="9">
+        <v>76</v>
+      </c>
+      <c r="G50" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>73.5</v>
+      </c>
+      <c r="F51" s="9">
+        <v>76</v>
+      </c>
+      <c r="G51" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>73.5</v>
+      </c>
+      <c r="F52" s="9">
+        <v>76</v>
+      </c>
+      <c r="G52" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>73.5</v>
+      </c>
+      <c r="F53" s="9">
+        <v>76</v>
+      </c>
+      <c r="G53" s="9">
         <v>75</v>
       </c>
     </row>
@@ -4948,19 +5415,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{075E49D7-A50C-4EF3-8D98-3E3352C23834}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4983,7 +5450,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -5006,7 +5473,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -5029,7 +5496,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -5052,7 +5519,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -5075,7 +5542,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -5098,7 +5565,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -5121,7 +5588,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -5144,7 +5611,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -5167,7 +5634,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -5190,7 +5657,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -5213,7 +5680,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -5236,7 +5703,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -5259,7 +5726,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -5282,7 +5749,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -5305,7 +5772,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -5328,7 +5795,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -5351,7 +5818,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -5374,7 +5841,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -5397,7 +5864,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -5420,7 +5887,7 @@
         <v>55.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -5443,7 +5910,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -5466,7 +5933,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -5489,7 +5956,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -5512,7 +5979,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -5535,7 +6002,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -5558,7 +6025,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -5581,7 +6048,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -5604,7 +6071,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -5627,7 +6094,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -5650,7 +6117,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -5673,7 +6140,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -5696,7 +6163,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -5719,7 +6186,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -5742,7 +6209,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -5765,7 +6232,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -5788,7 +6255,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -5811,7 +6278,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -5834,7 +6301,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -5857,7 +6324,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -5880,7 +6347,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -5903,7 +6370,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -5926,7 +6393,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -5949,7 +6416,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -5972,7 +6439,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -5995,7 +6462,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -6018,7 +6485,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -6041,7 +6508,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -6061,6 +6528,121 @@
         <v>131</v>
       </c>
       <c r="G48" s="9">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>125.5</v>
+      </c>
+      <c r="F49" s="9">
+        <v>131</v>
+      </c>
+      <c r="G49" s="9">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>125.5</v>
+      </c>
+      <c r="F50" s="9">
+        <v>131</v>
+      </c>
+      <c r="G50" s="9">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>125.5</v>
+      </c>
+      <c r="F51" s="9">
+        <v>131</v>
+      </c>
+      <c r="G51" s="9">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>125.5</v>
+      </c>
+      <c r="F52" s="9">
+        <v>131</v>
+      </c>
+      <c r="G52" s="9">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>125.5</v>
+      </c>
+      <c r="F53" s="9">
+        <v>131</v>
+      </c>
+      <c r="G53" s="9">
         <v>128</v>
       </c>
     </row>
@@ -6072,19 +6654,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18515E64-A7B9-4EA8-8571-9A16CD6B2FD3}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6107,7 +6689,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -6130,7 +6712,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -6153,7 +6735,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -6176,7 +6758,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -6199,7 +6781,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -6222,7 +6804,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -6245,7 +6827,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -6268,7 +6850,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -6291,7 +6873,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -6314,7 +6896,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -6337,7 +6919,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -6360,7 +6942,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -6383,7 +6965,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -6406,7 +6988,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -6429,7 +7011,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -6452,7 +7034,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -6475,7 +7057,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -6498,7 +7080,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -6521,7 +7103,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -6544,7 +7126,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -6567,7 +7149,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -6590,7 +7172,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -6613,7 +7195,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -6636,7 +7218,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -6659,7 +7241,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -6682,7 +7264,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -6705,7 +7287,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -6728,7 +7310,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -6751,7 +7333,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -6774,7 +7356,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -6797,7 +7379,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -6820,7 +7402,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -6843,7 +7425,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -6866,7 +7448,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -6889,7 +7471,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -6912,7 +7494,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -6935,7 +7517,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -6958,7 +7540,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -6981,7 +7563,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -7004,7 +7586,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -7027,7 +7609,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -7050,7 +7632,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -7073,7 +7655,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -7096,7 +7678,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -7119,7 +7701,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -7142,7 +7724,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -7165,7 +7747,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -7185,6 +7767,121 @@
         <v>202</v>
       </c>
       <c r="G48" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>199</v>
+      </c>
+      <c r="F49" s="9">
+        <v>202</v>
+      </c>
+      <c r="G49" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>199</v>
+      </c>
+      <c r="F50" s="9">
+        <v>202</v>
+      </c>
+      <c r="G50" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>199</v>
+      </c>
+      <c r="F51" s="9">
+        <v>202</v>
+      </c>
+      <c r="G51" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>199</v>
+      </c>
+      <c r="F52" s="9">
+        <v>202</v>
+      </c>
+      <c r="G52" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>199</v>
+      </c>
+      <c r="F53" s="9">
+        <v>202</v>
+      </c>
+      <c r="G53" s="9">
         <v>200</v>
       </c>
     </row>
@@ -7196,19 +7893,19 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8286ED8B-68EC-4D79-8787-976F03BA0C32}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7231,7 +7928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -7254,7 +7951,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -7277,7 +7974,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -7300,7 +7997,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -7323,7 +8020,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -7346,7 +8043,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -7369,7 +8066,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -7392,7 +8089,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -7415,7 +8112,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -7438,7 +8135,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -7461,7 +8158,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -7484,7 +8181,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -7507,7 +8204,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -7530,7 +8227,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -7553,7 +8250,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -7576,7 +8273,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -7599,7 +8296,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -7622,7 +8319,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -7645,7 +8342,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -7668,7 +8365,7 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -7691,7 +8388,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -7714,7 +8411,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -7737,7 +8434,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -7760,7 +8457,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -7783,7 +8480,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -7806,7 +8503,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -7829,7 +8526,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -7852,7 +8549,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -7875,7 +8572,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -7898,7 +8595,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -7921,7 +8618,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -7944,7 +8641,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -7967,7 +8664,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -7990,7 +8687,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -8013,7 +8710,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -8036,7 +8733,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -8059,7 +8756,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -8082,7 +8779,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -8105,7 +8802,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -8128,7 +8825,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -8151,7 +8848,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -8174,7 +8871,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -8197,7 +8894,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -8220,7 +8917,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -8243,7 +8940,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -8266,7 +8963,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -8289,7 +8986,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -8310,6 +9007,121 @@
       </c>
       <c r="G48" s="9">
         <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>140</v>
+      </c>
+      <c r="F49" s="9">
+        <v>144</v>
+      </c>
+      <c r="G49" s="9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>140</v>
+      </c>
+      <c r="F50" s="9">
+        <v>144</v>
+      </c>
+      <c r="G50" s="9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>140</v>
+      </c>
+      <c r="F51" s="9">
+        <v>144</v>
+      </c>
+      <c r="G51" s="9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>140</v>
+      </c>
+      <c r="F52" s="9">
+        <v>144</v>
+      </c>
+      <c r="G52" s="9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>140</v>
+      </c>
+      <c r="F53" s="9">
+        <v>144</v>
+      </c>
+      <c r="G53" s="9">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -8320,19 +9132,20 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62752974-E8DF-439D-ACF9-ECD10A65F3F8}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.8984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.3984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8355,7 +9168,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -8378,7 +9191,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -8401,7 +9214,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -8424,7 +9237,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -8447,7 +9260,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -8470,7 +9283,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -8493,7 +9306,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -8516,7 +9329,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -8539,7 +9352,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -8562,7 +9375,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -8585,7 +9398,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -8608,7 +9421,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -8631,7 +9444,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -8654,7 +9467,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -8677,7 +9490,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -8700,7 +9513,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -8723,7 +9536,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -8746,7 +9559,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -8769,7 +9582,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -8792,7 +9605,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -8815,7 +9628,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -8838,7 +9651,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -8861,7 +9674,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -8884,7 +9697,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -8907,7 +9720,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -8930,7 +9743,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -8953,7 +9766,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -8976,7 +9789,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -8999,7 +9812,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -9022,7 +9835,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -9045,7 +9858,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -9068,7 +9881,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -9091,7 +9904,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -9114,7 +9927,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -9137,7 +9950,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -9160,7 +9973,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -9183,7 +9996,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -9206,7 +10019,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -9229,7 +10042,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -9252,7 +10065,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -9275,7 +10088,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -9298,7 +10111,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -9321,7 +10134,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -9344,7 +10157,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -9367,7 +10180,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -9390,7 +10203,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -9413,7 +10226,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -9433,6 +10246,121 @@
         <v>231</v>
       </c>
       <c r="G48" s="12">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="12">
+        <v>228</v>
+      </c>
+      <c r="F49" s="12">
+        <v>231</v>
+      </c>
+      <c r="G49" s="12">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="12">
+        <v>228</v>
+      </c>
+      <c r="F50" s="12">
+        <v>231</v>
+      </c>
+      <c r="G50" s="12">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="12">
+        <v>228</v>
+      </c>
+      <c r="F51" s="12">
+        <v>231</v>
+      </c>
+      <c r="G51" s="12">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="12">
+        <v>228</v>
+      </c>
+      <c r="F52" s="12">
+        <v>231</v>
+      </c>
+      <c r="G52" s="12">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="12">
+        <v>228</v>
+      </c>
+      <c r="F53" s="12">
+        <v>231</v>
+      </c>
+      <c r="G53" s="12">
         <v>230</v>
       </c>
     </row>
@@ -9444,19 +10372,19 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9F2B4-31D6-4C55-BAC0-7D448A9FC534}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.21875" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="7.59765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9479,7 +10407,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -9502,7 +10430,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -9525,7 +10453,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -9548,7 +10476,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -9571,7 +10499,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -9594,7 +10522,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -9617,7 +10545,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -9640,7 +10568,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -9663,7 +10591,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -9686,7 +10614,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -9709,7 +10637,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -9732,7 +10660,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -9755,7 +10683,7 @@
         <v>126.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -9778,7 +10706,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -9801,7 +10729,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -9824,7 +10752,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -9847,7 +10775,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -9870,7 +10798,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -9893,7 +10821,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -9916,7 +10844,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -9939,7 +10867,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -9962,7 +10890,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -9985,7 +10913,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -10008,7 +10936,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -10031,7 +10959,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -10054,7 +10982,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -10077,7 +11005,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -10100,7 +11028,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -10123,7 +11051,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -10146,7 +11074,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -10169,7 +11097,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -10192,7 +11120,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -10215,7 +11143,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -10238,7 +11166,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -10261,7 +11189,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -10284,7 +11212,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -10307,7 +11235,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -10330,7 +11258,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -10353,7 +11281,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -10376,7 +11304,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -10399,7 +11327,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -10422,7 +11350,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -10445,7 +11373,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -10468,7 +11396,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -10491,7 +11419,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -10514,7 +11442,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -10537,7 +11465,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -10557,6 +11485,121 @@
         <v>405</v>
       </c>
       <c r="G48" s="14">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="14">
+        <v>398</v>
+      </c>
+      <c r="F49" s="14">
+        <v>405</v>
+      </c>
+      <c r="G49" s="14">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="14">
+        <v>398</v>
+      </c>
+      <c r="F50" s="14">
+        <v>405</v>
+      </c>
+      <c r="G50" s="14">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="14">
+        <v>398</v>
+      </c>
+      <c r="F51" s="14">
+        <v>405</v>
+      </c>
+      <c r="G51" s="14">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="14">
+        <v>398</v>
+      </c>
+      <c r="F52" s="14">
+        <v>405</v>
+      </c>
+      <c r="G52" s="14">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="14">
+        <v>398</v>
+      </c>
+      <c r="F53" s="14">
+        <v>405</v>
+      </c>
+      <c r="G53" s="14">
         <v>400</v>
       </c>
     </row>
